--- a/understat_all_leagues_advanced.xlsx
+++ b/understat_all_leagues_advanced.xlsx
@@ -1380,94 +1380,94 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Deportivo La Coruna</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11.61</v>
+        <v>12.03</v>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>12.19</v>
       </c>
       <c r="F9" t="n">
         <v>1.35</v>
       </c>
       <c r="G9" t="n">
-        <v>10.92</v>
+        <v>12.35</v>
       </c>
       <c r="H9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>10.46</v>
+        <v>11.61</v>
       </c>
       <c r="E10" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="G10" t="n">
-        <v>12.51</v>
+        <v>10.92</v>
       </c>
       <c r="H10" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.91</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deportivo La Coruna</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>9.9</v>
+        <v>10.46</v>
       </c>
       <c r="E11" t="n">
-        <v>10.73</v>
+        <v>10.6</v>
       </c>
       <c r="F11" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="G11" t="n">
-        <v>11.78</v>
+        <v>12.51</v>
       </c>
       <c r="H11" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.05</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="12">
@@ -1628,94 +1628,94 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="n">
         <v>7</v>
       </c>
-      <c r="C17" t="n">
-        <v>8</v>
-      </c>
       <c r="D17" t="n">
-        <v>7.69</v>
+        <v>7.73</v>
       </c>
       <c r="E17" t="n">
-        <v>9.119999999999999</v>
+        <v>11.88</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="G17" t="n">
-        <v>13.03</v>
+        <v>17.96</v>
       </c>
       <c r="H17" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.91</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="n">
         <v>8</v>
       </c>
-      <c r="C18" t="n">
-        <v>5</v>
-      </c>
       <c r="D18" t="n">
-        <v>7.5</v>
+        <v>7.69</v>
       </c>
       <c r="E18" t="n">
-        <v>7.44</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.93</v>
+        <v>1.3</v>
       </c>
       <c r="G18" t="n">
-        <v>14.08</v>
+        <v>13.03</v>
       </c>
       <c r="H18" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="I18" t="n">
-        <v>-6.64</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>7.12</v>
+        <v>7.5</v>
       </c>
       <c r="E19" t="n">
-        <v>11.32</v>
+        <v>7.44</v>
       </c>
       <c r="F19" t="n">
-        <v>1.62</v>
+        <v>0.93</v>
       </c>
       <c r="G19" t="n">
-        <v>16.5</v>
+        <v>14.08</v>
       </c>
       <c r="H19" t="n">
-        <v>2.36</v>
+        <v>1.76</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.18</v>
+        <v>-6.64</v>
       </c>
     </row>
     <row r="20">
@@ -2127,28 +2127,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>8.52</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>10.65</v>
+        <v>12.47</v>
       </c>
       <c r="F11" t="n">
         <v>1.78</v>
       </c>
       <c r="G11" t="n">
-        <v>10.1</v>
+        <v>13.04</v>
       </c>
       <c r="H11" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="I11" t="n">
-        <v>0.55</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="12">
@@ -2185,156 +2185,156 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>7.19</v>
+        <v>7.42</v>
       </c>
       <c r="E13" t="n">
-        <v>8.44</v>
+        <v>11.84</v>
       </c>
       <c r="F13" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="G13" t="n">
-        <v>10.98</v>
+        <v>16.35</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83</v>
+        <v>2.34</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.54</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>6.74</v>
+        <v>7.19</v>
       </c>
       <c r="E14" t="n">
-        <v>11.72</v>
+        <v>8.44</v>
       </c>
       <c r="F14" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="G14" t="n">
-        <v>15.29</v>
+        <v>10.98</v>
       </c>
       <c r="H14" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.57</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6.44</v>
+        <v>6.74</v>
       </c>
       <c r="E15" t="n">
-        <v>6.19</v>
+        <v>11.72</v>
       </c>
       <c r="F15" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="G15" t="n">
-        <v>8.67</v>
+        <v>15.29</v>
       </c>
       <c r="H15" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.48</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>6.03</v>
+        <v>6.44</v>
       </c>
       <c r="E16" t="n">
-        <v>6.26</v>
+        <v>6.19</v>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="G16" t="n">
-        <v>11.15</v>
+        <v>8.67</v>
       </c>
       <c r="H16" t="n">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.89</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>5.28</v>
+        <v>6.03</v>
       </c>
       <c r="E17" t="n">
-        <v>8.9</v>
+        <v>6.26</v>
       </c>
       <c r="F17" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>14.53</v>
+        <v>11.15</v>
       </c>
       <c r="H17" t="n">
-        <v>2.42</v>
+        <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.63</v>
+        <v>-4.89</v>
       </c>
     </row>
     <row r="18">
@@ -2715,90 +2715,90 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>7.53</v>
+        <v>8.69</v>
       </c>
       <c r="E8" t="n">
-        <v>10.49</v>
+        <v>11.51</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="G8" t="n">
-        <v>9.74</v>
+        <v>11.01</v>
       </c>
       <c r="H8" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="I8" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>6.62</v>
+        <v>7.31</v>
       </c>
       <c r="E9" t="n">
-        <v>9.65</v>
+        <v>12.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="G9" t="n">
-        <v>9.859999999999999</v>
+        <v>14.66</v>
       </c>
       <c r="H9" t="n">
-        <v>1.97</v>
+        <v>2.44</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.21</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>5.77</v>
+        <v>6.62</v>
       </c>
       <c r="E10" t="n">
-        <v>10.83</v>
+        <v>9.65</v>
       </c>
       <c r="F10" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="G10" t="n">
-        <v>13.64</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>2.73</v>
+        <v>1.97</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.81</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="11">
@@ -3144,156 +3144,156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>12.84</v>
+        <v>12.99</v>
       </c>
       <c r="E2" t="n">
-        <v>10.33</v>
+        <v>14.07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="G2" t="n">
-        <v>3.77</v>
+        <v>10.14</v>
       </c>
       <c r="H2" t="n">
-        <v>0.63</v>
+        <v>1.45</v>
       </c>
       <c r="I2" t="n">
-        <v>6.56</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>12.59</v>
+        <v>12.84</v>
       </c>
       <c r="E3" t="n">
-        <v>14.88</v>
+        <v>10.33</v>
       </c>
       <c r="F3" t="n">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="G3" t="n">
-        <v>6.98</v>
+        <v>3.77</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16</v>
+        <v>0.63</v>
       </c>
       <c r="I3" t="n">
-        <v>7.9</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>11.93</v>
+        <v>12.59</v>
       </c>
       <c r="E4" t="n">
-        <v>15.67</v>
+        <v>14.88</v>
       </c>
       <c r="F4" t="n">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
-        <v>9.050000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="H4" t="n">
-        <v>1.51</v>
+        <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>6.62</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10.5</v>
+        <v>11.93</v>
       </c>
       <c r="E5" t="n">
-        <v>13.91</v>
+        <v>15.67</v>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.61</v>
       </c>
       <c r="G5" t="n">
-        <v>9.32</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="I5" t="n">
-        <v>4.59</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="E6" t="n">
-        <v>12.01</v>
+        <v>13.91</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="G6" t="n">
-        <v>9.529999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="H6" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="I6" t="n">
-        <v>2.48</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="7">
@@ -3582,28 +3582,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>5.59</v>
+        <v>5.93</v>
       </c>
       <c r="E16" t="n">
-        <v>10.01</v>
+        <v>10.62</v>
       </c>
       <c r="F16" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="G16" t="n">
-        <v>14.69</v>
+        <v>16.75</v>
       </c>
       <c r="H16" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.68</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="17">

--- a/understat_all_leagues_advanced.xlsx
+++ b/understat_all_leagues_advanced.xlsx
@@ -482,63 +482,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>11.99</v>
+        <v>14.49</v>
       </c>
       <c r="E2" t="n">
-        <v>11.73</v>
+        <v>16.64</v>
       </c>
       <c r="F2" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="G2" t="n">
-        <v>6.65</v>
+        <v>9.31</v>
       </c>
       <c r="H2" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>5.08</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>11.72</v>
+        <v>11.99</v>
       </c>
       <c r="E3" t="n">
-        <v>12.63</v>
+        <v>11.73</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="G3" t="n">
-        <v>7.94</v>
+        <v>6.65</v>
       </c>
       <c r="H3" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="I3" t="n">
-        <v>4.69</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="4">
@@ -606,466 +606,466 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>9.859999999999999</v>
+        <v>10.47</v>
       </c>
       <c r="E6" t="n">
-        <v>11.15</v>
+        <v>10.55</v>
       </c>
       <c r="F6" t="n">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="G6" t="n">
-        <v>8.73</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="I6" t="n">
-        <v>2.42</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>9.4</v>
+        <v>10.42</v>
       </c>
       <c r="E7" t="n">
-        <v>11.8</v>
+        <v>11.72</v>
       </c>
       <c r="F7" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>9.33</v>
+        <v>10.33</v>
       </c>
       <c r="H7" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>2.47</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>9.35</v>
+        <v>10.23</v>
       </c>
       <c r="E8" t="n">
-        <v>9.77</v>
+        <v>12.65</v>
       </c>
       <c r="F8" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="G8" t="n">
-        <v>8.369999999999999</v>
+        <v>10.88</v>
       </c>
       <c r="H8" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>8.9</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>11.45</v>
+        <v>12.02</v>
       </c>
       <c r="F9" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="G9" t="n">
-        <v>9.25</v>
+        <v>11.82</v>
       </c>
       <c r="H9" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>8.56</v>
+        <v>9.41</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>11.92</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>8.529999999999999</v>
+        <v>12.54</v>
       </c>
       <c r="H10" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="I10" t="n">
-        <v>0.47</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>8.449999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="E11" t="n">
-        <v>10.94</v>
+        <v>9.77</v>
       </c>
       <c r="F11" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="G11" t="n">
-        <v>10.49</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="I11" t="n">
-        <v>0.45</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>7.86</v>
+        <v>8.9</v>
       </c>
       <c r="E12" t="n">
-        <v>8.42</v>
+        <v>11.45</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="G12" t="n">
-        <v>8.73</v>
+        <v>9.25</v>
       </c>
       <c r="H12" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.31</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>7.7</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>7.85</v>
+        <v>10.94</v>
       </c>
       <c r="F13" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="G13" t="n">
-        <v>10.06</v>
+        <v>10.49</v>
       </c>
       <c r="H13" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.21</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>7.21</v>
+        <v>7.97</v>
       </c>
       <c r="E14" t="n">
-        <v>10.32</v>
+        <v>8.91</v>
       </c>
       <c r="F14" t="n">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="G14" t="n">
-        <v>11.97</v>
+        <v>13.06</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.65</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>6.82</v>
+        <v>7.86</v>
       </c>
       <c r="E15" t="n">
-        <v>9.74</v>
+        <v>8.42</v>
       </c>
       <c r="F15" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>11.69</v>
+        <v>8.73</v>
       </c>
       <c r="H15" t="n">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.95</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>6.68</v>
+        <v>7.7</v>
       </c>
       <c r="E16" t="n">
-        <v>8.380000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="G16" t="n">
-        <v>12.09</v>
+        <v>10.06</v>
       </c>
       <c r="H16" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.71</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>6.08</v>
+        <v>6.84</v>
       </c>
       <c r="E17" t="n">
-        <v>7.76</v>
+        <v>9.75</v>
       </c>
       <c r="F17" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>16.09</v>
       </c>
       <c r="H17" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.24</v>
+        <v>-6.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>6.05</v>
+        <v>6.67</v>
       </c>
       <c r="E18" t="n">
-        <v>7.26</v>
+        <v>8.68</v>
       </c>
       <c r="F18" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="G18" t="n">
-        <v>9.98</v>
+        <v>13.09</v>
       </c>
       <c r="H18" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.72</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>5.99</v>
+        <v>6.15</v>
       </c>
       <c r="E19" t="n">
-        <v>9.83</v>
+        <v>7.39</v>
       </c>
       <c r="F19" t="n">
-        <v>1.64</v>
+        <v>1.06</v>
       </c>
       <c r="G19" t="n">
-        <v>13.78</v>
+        <v>12.26</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.95</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>5.75</v>
+        <v>5.99</v>
       </c>
       <c r="E20" t="n">
-        <v>6.83</v>
+        <v>9.83</v>
       </c>
       <c r="F20" t="n">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="G20" t="n">
-        <v>12.14</v>
+        <v>13.78</v>
       </c>
       <c r="H20" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="I20" t="n">
-        <v>-5.31</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="21">
@@ -1167,28 +1167,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>21.34</v>
+        <v>23.9</v>
       </c>
       <c r="E2" t="n">
-        <v>32.32</v>
+        <v>35.5</v>
       </c>
       <c r="F2" t="n">
-        <v>4.04</v>
+        <v>3.94</v>
       </c>
       <c r="G2" t="n">
-        <v>7.94</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="I2" t="n">
-        <v>24.38</v>
+        <v>26.21</v>
       </c>
     </row>
     <row r="3">
@@ -1229,28 +1229,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>14.9</v>
+        <v>17.28</v>
       </c>
       <c r="E4" t="n">
-        <v>15.7</v>
+        <v>17.48</v>
       </c>
       <c r="F4" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G4" t="n">
-        <v>9.48</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>6.22</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="5">
@@ -1260,28 +1260,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>13.94</v>
+        <v>16.69</v>
       </c>
       <c r="E5" t="n">
-        <v>20.14</v>
+        <v>22.43</v>
       </c>
       <c r="F5" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="G5" t="n">
-        <v>12.86</v>
+        <v>13.08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="I5" t="n">
-        <v>7.28</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="6">
@@ -1291,28 +1291,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
         <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>12.21</v>
+        <v>12.52</v>
       </c>
       <c r="E6" t="n">
-        <v>15.81</v>
+        <v>17.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
-        <v>13.93</v>
+        <v>17.12</v>
       </c>
       <c r="H6" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.88</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="7">
@@ -1322,28 +1322,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>12.18</v>
+        <v>12.47</v>
       </c>
       <c r="E7" t="n">
-        <v>11.28</v>
+        <v>11.8</v>
       </c>
       <c r="F7" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="G7" t="n">
-        <v>7.7</v>
+        <v>9.94</v>
       </c>
       <c r="H7" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="I7" t="n">
-        <v>3.58</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="8">
@@ -1380,63 +1380,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deportivo La Coruna</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>12.03</v>
+        <v>12.04</v>
       </c>
       <c r="E9" t="n">
-        <v>12.19</v>
+        <v>11.29</v>
       </c>
       <c r="F9" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
-        <v>12.35</v>
+        <v>12.7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.16</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Deportivo La Coruna</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11.61</v>
+        <v>12.03</v>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>12.19</v>
       </c>
       <c r="F10" t="n">
         <v>1.35</v>
       </c>
       <c r="G10" t="n">
-        <v>10.92</v>
+        <v>12.35</v>
       </c>
       <c r="H10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="11">
@@ -1473,38 +1473,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>9.699999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="E12" t="n">
-        <v>8.039999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="G12" t="n">
-        <v>9.92</v>
+        <v>14.59</v>
       </c>
       <c r="H12" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.88</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1514,28 +1514,28 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>9.59</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>10.03</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>14.63</v>
+        <v>9.92</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.6</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1545,22 +1545,22 @@
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>9.140000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="E14" t="n">
-        <v>11.21</v>
+        <v>10.03</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="G14" t="n">
-        <v>17.74</v>
+        <v>14.63</v>
       </c>
       <c r="H14" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.53</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="15">
@@ -1570,152 +1570,152 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>9.09</v>
+        <v>9.24</v>
       </c>
       <c r="E15" t="n">
-        <v>10.55</v>
+        <v>10.78</v>
       </c>
       <c r="F15" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="G15" t="n">
-        <v>16.12</v>
+        <v>18.42</v>
       </c>
       <c r="H15" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.57</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>8.640000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>10.69</v>
+        <v>11.21</v>
       </c>
       <c r="F16" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="G16" t="n">
-        <v>15.13</v>
+        <v>17.74</v>
       </c>
       <c r="H16" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.44</v>
+        <v>-6.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>7.73</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>11.88</v>
+        <v>10.69</v>
       </c>
       <c r="F17" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="G17" t="n">
-        <v>17.96</v>
+        <v>15.13</v>
       </c>
       <c r="H17" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.08</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" t="n">
         <v>7</v>
       </c>
-      <c r="C18" t="n">
-        <v>8</v>
-      </c>
       <c r="D18" t="n">
-        <v>7.69</v>
+        <v>7.73</v>
       </c>
       <c r="E18" t="n">
-        <v>9.119999999999999</v>
+        <v>11.88</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="G18" t="n">
-        <v>13.03</v>
+        <v>17.96</v>
       </c>
       <c r="H18" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.91</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" t="n">
-        <v>5</v>
-      </c>
       <c r="D19" t="n">
-        <v>7.5</v>
+        <v>7.69</v>
       </c>
       <c r="E19" t="n">
-        <v>7.44</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.93</v>
+        <v>1.3</v>
       </c>
       <c r="G19" t="n">
-        <v>14.08</v>
+        <v>13.03</v>
       </c>
       <c r="H19" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.64</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="20">
@@ -1844,94 +1844,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>14.65</v>
+        <v>16.44</v>
       </c>
       <c r="E2" t="n">
-        <v>11.61</v>
+        <v>22.06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.49</v>
+        <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>8.69</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>13.94</v>
+        <v>15.4</v>
       </c>
       <c r="E3" t="n">
-        <v>18.47</v>
+        <v>18.65</v>
       </c>
       <c r="F3" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>7.88</v>
+        <v>7.92</v>
       </c>
       <c r="H3" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="I3" t="n">
-        <v>10.59</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>13.24</v>
+        <v>14.65</v>
       </c>
       <c r="E4" t="n">
-        <v>17.24</v>
+        <v>11.61</v>
       </c>
       <c r="F4" t="n">
-        <v>2.87</v>
+        <v>1.93</v>
       </c>
       <c r="G4" t="n">
-        <v>7.41</v>
+        <v>2.92</v>
       </c>
       <c r="H4" t="n">
-        <v>1.24</v>
+        <v>0.49</v>
       </c>
       <c r="I4" t="n">
-        <v>9.83</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="5">
@@ -1941,28 +1941,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>11.69</v>
+        <v>14.28</v>
       </c>
       <c r="E5" t="n">
-        <v>12.42</v>
+        <v>14.97</v>
       </c>
       <c r="F5" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>8.08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="I5" t="n">
-        <v>5.02</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="6">
@@ -2034,28 +2034,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>10.03</v>
+        <v>10.41</v>
       </c>
       <c r="E8" t="n">
-        <v>9.17</v>
+        <v>10.94</v>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>7.24</v>
+        <v>10.84</v>
       </c>
       <c r="H8" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="I8" t="n">
-        <v>1.93</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -2251,28 +2251,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>6.74</v>
+        <v>7.02</v>
       </c>
       <c r="E15" t="n">
-        <v>11.72</v>
+        <v>12.41</v>
       </c>
       <c r="F15" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="G15" t="n">
-        <v>15.29</v>
+        <v>17.84</v>
       </c>
       <c r="H15" t="n">
         <v>2.55</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.57</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="16">
@@ -2282,28 +2282,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>6.44</v>
+        <v>7.01</v>
       </c>
       <c r="E16" t="n">
-        <v>6.19</v>
+        <v>6.7</v>
       </c>
       <c r="F16" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="G16" t="n">
-        <v>8.67</v>
+        <v>10.08</v>
       </c>
       <c r="H16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.48</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="17">
@@ -2529,96 +2529,96 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>13.67</v>
+        <v>16.63</v>
       </c>
       <c r="E2" t="n">
-        <v>17.9</v>
+        <v>22.81</v>
       </c>
       <c r="F2" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="n">
-        <v>4.96</v>
+        <v>5.66</v>
       </c>
       <c r="H2" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>12.94</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>11.23</v>
+        <v>12.01</v>
       </c>
       <c r="E3" t="n">
-        <v>10.26</v>
+        <v>12.2</v>
       </c>
       <c r="F3" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="G3" t="n">
-        <v>4.41</v>
+        <v>6.03</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>1.01</v>
       </c>
       <c r="I3" t="n">
-        <v>5.85</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>11.65</v>
       </c>
       <c r="E4" t="n">
-        <v>12.73</v>
+        <v>14.25</v>
       </c>
       <c r="F4" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6</v>
+        <v>8.9</v>
       </c>
       <c r="H4" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="I4" t="n">
-        <v>7.13</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2628,84 +2628,84 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>10.65</v>
+        <v>11.23</v>
       </c>
       <c r="E5" t="n">
-        <v>11.21</v>
+        <v>10.26</v>
       </c>
       <c r="F5" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1</v>
+        <v>4.41</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>6.11</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RasenBallsport Leipzig</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10.47</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="n">
-        <v>13.48</v>
+        <v>12.73</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="G6" t="n">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="I6" t="n">
-        <v>6.38</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RasenBallsport Leipzig</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9.33</v>
+        <v>10.49</v>
       </c>
       <c r="E7" t="n">
-        <v>12.72</v>
+        <v>14.18</v>
       </c>
       <c r="F7" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
-        <v>8.49</v>
+        <v>12.01</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.23</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="8">
@@ -2773,94 +2773,94 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>VfB Stuttgart</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6.62</v>
+        <v>7.25</v>
       </c>
       <c r="E10" t="n">
-        <v>9.65</v>
+        <v>13.33</v>
       </c>
       <c r="F10" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>9.859999999999999</v>
+        <v>15.77</v>
       </c>
       <c r="H10" t="n">
-        <v>1.97</v>
+        <v>2.63</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.21</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>5.26</v>
+        <v>7.19</v>
       </c>
       <c r="E11" t="n">
-        <v>10.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="G11" t="n">
-        <v>14.1</v>
+        <v>10.31</v>
       </c>
       <c r="H11" t="n">
-        <v>2.82</v>
+        <v>1.72</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.4</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>4.94</v>
+        <v>6.62</v>
       </c>
       <c r="E12" t="n">
-        <v>6.14</v>
+        <v>9.65</v>
       </c>
       <c r="F12" t="n">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="G12" t="n">
-        <v>8.94</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="13">
@@ -2870,183 +2870,183 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>4.87</v>
+        <v>6.12</v>
       </c>
       <c r="E13" t="n">
-        <v>10.52</v>
+        <v>14.26</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="G13" t="n">
-        <v>13.12</v>
+        <v>17.12</v>
       </c>
       <c r="H13" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.6</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
         <v>5</v>
       </c>
-      <c r="C14" t="n">
-        <v>6</v>
-      </c>
       <c r="D14" t="n">
-        <v>4.67</v>
+        <v>5.68</v>
       </c>
       <c r="E14" t="n">
-        <v>5.46</v>
+        <v>7.1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="G14" t="n">
-        <v>10.15</v>
+        <v>14.13</v>
       </c>
       <c r="H14" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.69</v>
+        <v>-7.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>4.62</v>
+        <v>5.48</v>
       </c>
       <c r="E15" t="n">
-        <v>6.95</v>
+        <v>7.13</v>
       </c>
       <c r="F15" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="G15" t="n">
-        <v>11.92</v>
+        <v>12.79</v>
       </c>
       <c r="H15" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.97</v>
+        <v>-5.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>4.37</v>
+        <v>5.44</v>
       </c>
       <c r="E16" t="n">
-        <v>6.16</v>
+        <v>10.54</v>
       </c>
       <c r="F16" t="n">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="G16" t="n">
-        <v>13.14</v>
+        <v>14.81</v>
       </c>
       <c r="H16" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.98</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
         <v>5</v>
       </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
       <c r="D17" t="n">
-        <v>4.03</v>
+        <v>5.07</v>
       </c>
       <c r="E17" t="n">
-        <v>5.17</v>
+        <v>7.36</v>
       </c>
       <c r="F17" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="G17" t="n">
-        <v>10.13</v>
+        <v>13.46</v>
       </c>
       <c r="H17" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.96</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
-        <v>7</v>
-      </c>
       <c r="D18" t="n">
-        <v>3.88</v>
+        <v>4.6</v>
       </c>
       <c r="E18" t="n">
         <v>6.54</v>
       </c>
       <c r="F18" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="G18" t="n">
-        <v>11.07</v>
+        <v>12.79</v>
       </c>
       <c r="H18" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.53</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="19">
@@ -3144,100 +3144,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>12.99</v>
+        <v>14.03</v>
       </c>
       <c r="E2" t="n">
-        <v>14.07</v>
+        <v>18.03</v>
       </c>
       <c r="F2" t="n">
-        <v>2.01</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>10.14</v>
+        <v>10.36</v>
       </c>
       <c r="H2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>3.93</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>12.84</v>
+        <v>13.04</v>
       </c>
       <c r="E3" t="n">
-        <v>10.33</v>
+        <v>15.67</v>
       </c>
       <c r="F3" t="n">
-        <v>1.72</v>
+        <v>2.24</v>
       </c>
       <c r="G3" t="n">
-        <v>3.77</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.63</v>
+        <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>6.56</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>12.59</v>
+        <v>12.99</v>
       </c>
       <c r="E4" t="n">
-        <v>14.88</v>
+        <v>14.07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>2.01</v>
       </c>
       <c r="G4" t="n">
-        <v>6.98</v>
+        <v>10.14</v>
       </c>
       <c r="H4" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>7.9</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3247,22 +3247,22 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11.93</v>
+        <v>12.84</v>
       </c>
       <c r="E5" t="n">
-        <v>15.67</v>
+        <v>10.33</v>
       </c>
       <c r="F5" t="n">
-        <v>2.61</v>
+        <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>9.050000000000001</v>
+        <v>3.77</v>
       </c>
       <c r="H5" t="n">
-        <v>1.51</v>
+        <v>0.63</v>
       </c>
       <c r="I5" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="6">
@@ -3272,152 +3272,152 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10.5</v>
+        <v>12.19</v>
       </c>
       <c r="E6" t="n">
-        <v>13.91</v>
+        <v>15.76</v>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="G6" t="n">
-        <v>9.32</v>
+        <v>10.79</v>
       </c>
       <c r="H6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I6" t="n">
-        <v>4.59</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>10.21</v>
+        <v>10.22</v>
       </c>
       <c r="E7" t="n">
-        <v>10.99</v>
+        <v>10.78</v>
       </c>
       <c r="F7" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="G7" t="n">
-        <v>7.31</v>
+        <v>10.53</v>
       </c>
       <c r="H7" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.68</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.21</v>
       </c>
       <c r="E8" t="n">
-        <v>13.43</v>
+        <v>10.99</v>
       </c>
       <c r="F8" t="n">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="G8" t="n">
-        <v>11.84</v>
+        <v>7.31</v>
       </c>
       <c r="H8" t="n">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="I8" t="n">
-        <v>1.59</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>7.99</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>13.43</v>
       </c>
       <c r="F9" t="n">
-        <v>1.23</v>
+        <v>2.24</v>
       </c>
       <c r="G9" t="n">
-        <v>7.98</v>
+        <v>11.84</v>
       </c>
       <c r="H9" t="n">
-        <v>1.33</v>
+        <v>1.97</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.58</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>7.86</v>
+        <v>7.99</v>
       </c>
       <c r="E10" t="n">
-        <v>8.73</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="G10" t="n">
-        <v>9.74</v>
+        <v>7.98</v>
       </c>
       <c r="H10" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.01</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="11">
@@ -3578,125 +3578,125 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>5.93</v>
+        <v>6.27</v>
       </c>
       <c r="E16" t="n">
-        <v>10.62</v>
+        <v>8.91</v>
       </c>
       <c r="F16" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="G16" t="n">
-        <v>16.75</v>
+        <v>13.64</v>
       </c>
       <c r="H16" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.13</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>5.34</v>
+        <v>5.93</v>
       </c>
       <c r="E17" t="n">
-        <v>7.4</v>
+        <v>10.62</v>
       </c>
       <c r="F17" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="G17" t="n">
-        <v>11.61</v>
+        <v>16.75</v>
       </c>
       <c r="H17" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.21</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>5.23</v>
+        <v>5.71</v>
       </c>
       <c r="E18" t="n">
-        <v>7.44</v>
+        <v>8.23</v>
       </c>
       <c r="F18" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="G18" t="n">
-        <v>11.79</v>
+        <v>13.53</v>
       </c>
       <c r="H18" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.35</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>5.02</v>
+        <v>5.34</v>
       </c>
       <c r="E19" t="n">
-        <v>6.91</v>
+        <v>7.4</v>
       </c>
       <c r="F19" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="G19" t="n">
-        <v>11.17</v>
+        <v>11.61</v>
       </c>
       <c r="H19" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.26</v>
+        <v>-4.21</v>
       </c>
     </row>
   </sheetData>

--- a/understat_all_leagues_advanced.xlsx
+++ b/understat_all_leagues_advanced.xlsx
@@ -513,162 +513,162 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>11.99</v>
+        <v>13.83</v>
       </c>
       <c r="E3" t="n">
-        <v>11.73</v>
+        <v>16.79</v>
       </c>
       <c r="F3" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>6.65</v>
+        <v>10.12</v>
       </c>
       <c r="H3" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="I3" t="n">
-        <v>5.08</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>11.42</v>
+        <v>13.48</v>
       </c>
       <c r="E4" t="n">
-        <v>12.24</v>
+        <v>12.65</v>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="G4" t="n">
-        <v>7.26</v>
+        <v>7.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.98</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>11.19</v>
+        <v>12.58</v>
       </c>
       <c r="E5" t="n">
-        <v>14.53</v>
+        <v>12.99</v>
       </c>
       <c r="F5" t="n">
-        <v>2.42</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
-        <v>9.5</v>
+        <v>8.17</v>
       </c>
       <c r="H5" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>5.03</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>10.47</v>
+        <v>12.34</v>
       </c>
       <c r="E6" t="n">
-        <v>10.55</v>
+        <v>14.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>9.380000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="I6" t="n">
-        <v>1.17</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>10.42</v>
+        <v>10.47</v>
       </c>
       <c r="E7" t="n">
-        <v>11.72</v>
+        <v>10.55</v>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="G7" t="n">
-        <v>10.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="I7" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -678,239 +678,239 @@
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10.23</v>
+        <v>10.42</v>
       </c>
       <c r="E8" t="n">
-        <v>12.65</v>
+        <v>11.72</v>
       </c>
       <c r="F8" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>10.88</v>
+        <v>10.33</v>
       </c>
       <c r="H8" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9.640000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="E9" t="n">
-        <v>12.02</v>
+        <v>12.65</v>
       </c>
       <c r="F9" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="G9" t="n">
-        <v>11.82</v>
+        <v>10.88</v>
       </c>
       <c r="H9" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>9.41</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>11.92</v>
+        <v>12.53</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="G10" t="n">
-        <v>12.54</v>
+        <v>10.66</v>
       </c>
       <c r="H10" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.62</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>9.35</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>9.77</v>
+        <v>12.02</v>
       </c>
       <c r="F11" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="G11" t="n">
-        <v>8.369999999999999</v>
+        <v>11.82</v>
       </c>
       <c r="H11" t="n">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="E12" t="n">
-        <v>11.45</v>
+        <v>9.83</v>
       </c>
       <c r="F12" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>9.25</v>
+        <v>9.81</v>
       </c>
       <c r="H12" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>8.449999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="E13" t="n">
-        <v>10.94</v>
+        <v>11.92</v>
       </c>
       <c r="F13" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>10.49</v>
+        <v>12.54</v>
       </c>
       <c r="H13" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="I13" t="n">
-        <v>0.45</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>7.97</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>8.91</v>
+        <v>11.04</v>
       </c>
       <c r="F14" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="G14" t="n">
-        <v>13.06</v>
+        <v>14.88</v>
       </c>
       <c r="H14" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.15</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>7.86</v>
+        <v>7.97</v>
       </c>
       <c r="E15" t="n">
-        <v>8.42</v>
+        <v>8.91</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="G15" t="n">
-        <v>8.73</v>
+        <v>13.06</v>
       </c>
       <c r="H15" t="n">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.31</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="16">
@@ -1009,63 +1009,63 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>6.15</v>
+        <v>6.22</v>
       </c>
       <c r="E19" t="n">
-        <v>7.39</v>
+        <v>10.46</v>
       </c>
       <c r="F19" t="n">
-        <v>1.06</v>
+        <v>1.49</v>
       </c>
       <c r="G19" t="n">
-        <v>12.26</v>
+        <v>16.04</v>
       </c>
       <c r="H19" t="n">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.87</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>5.99</v>
+        <v>6.15</v>
       </c>
       <c r="E20" t="n">
-        <v>9.83</v>
+        <v>7.39</v>
       </c>
       <c r="F20" t="n">
-        <v>1.64</v>
+        <v>1.06</v>
       </c>
       <c r="G20" t="n">
-        <v>13.78</v>
+        <v>12.26</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.95</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="21">
@@ -1198,28 +1198,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>18.63</v>
+        <v>20.62</v>
       </c>
       <c r="E3" t="n">
-        <v>21.09</v>
+        <v>23.21</v>
       </c>
       <c r="F3" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>8.300000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I3" t="n">
-        <v>12.79</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="4">
@@ -1287,218 +1287,218 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>12.52</v>
+        <v>13.86</v>
       </c>
       <c r="E6" t="n">
-        <v>17.16</v>
+        <v>12.84</v>
       </c>
       <c r="F6" t="n">
-        <v>1.91</v>
+        <v>1.43</v>
       </c>
       <c r="G6" t="n">
-        <v>17.12</v>
+        <v>10.37</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9</v>
+        <v>1.15</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>12.47</v>
+        <v>12.52</v>
       </c>
       <c r="E7" t="n">
-        <v>11.8</v>
+        <v>17.16</v>
       </c>
       <c r="F7" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="G7" t="n">
-        <v>9.94</v>
+        <v>17.12</v>
       </c>
       <c r="H7" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.86</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>12.17</v>
+        <v>12.51</v>
       </c>
       <c r="E8" t="n">
-        <v>11.66</v>
+        <v>13.11</v>
       </c>
       <c r="F8" t="n">
         <v>1.46</v>
       </c>
       <c r="G8" t="n">
-        <v>9.609999999999999</v>
+        <v>14.85</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="I8" t="n">
-        <v>2.05</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
         <v>9</v>
       </c>
-      <c r="C9" t="n">
-        <v>8</v>
-      </c>
       <c r="D9" t="n">
-        <v>12.04</v>
+        <v>12.47</v>
       </c>
       <c r="E9" t="n">
-        <v>11.29</v>
+        <v>11.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>12.7</v>
+        <v>9.94</v>
       </c>
       <c r="H9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.41</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deportivo La Coruna</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>12.03</v>
+        <v>12.04</v>
       </c>
       <c r="E10" t="n">
-        <v>12.19</v>
+        <v>11.29</v>
       </c>
       <c r="F10" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="G10" t="n">
-        <v>12.35</v>
+        <v>12.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.16</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo La Coruna</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>10.46</v>
+        <v>12.03</v>
       </c>
       <c r="E11" t="n">
-        <v>10.6</v>
+        <v>12.19</v>
       </c>
       <c r="F11" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="G11" t="n">
-        <v>12.51</v>
+        <v>12.35</v>
       </c>
       <c r="H11" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.91</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>10.07</v>
+        <v>11.23</v>
       </c>
       <c r="E12" t="n">
-        <v>9.69</v>
+        <v>11.92</v>
       </c>
       <c r="F12" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="G12" t="n">
-        <v>14.59</v>
+        <v>14.64</v>
       </c>
       <c r="H12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.9</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="13">
@@ -1508,152 +1508,152 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>9.699999999999999</v>
+        <v>10.68</v>
       </c>
       <c r="E13" t="n">
-        <v>8.039999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G13" t="n">
-        <v>9.92</v>
+        <v>11.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.88</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>9.59</v>
+        <v>10.44</v>
       </c>
       <c r="E14" t="n">
-        <v>10.03</v>
+        <v>13.26</v>
       </c>
       <c r="F14" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="G14" t="n">
-        <v>14.63</v>
+        <v>17.06</v>
       </c>
       <c r="H14" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.6</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>9.24</v>
+        <v>10.07</v>
       </c>
       <c r="E15" t="n">
-        <v>10.78</v>
+        <v>9.69</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="G15" t="n">
-        <v>18.42</v>
+        <v>14.59</v>
       </c>
       <c r="H15" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.64</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>9.140000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="E16" t="n">
-        <v>11.21</v>
+        <v>10.78</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>17.74</v>
+        <v>18.42</v>
       </c>
       <c r="H16" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.53</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" t="n">
         <v>8</v>
       </c>
-      <c r="C17" t="n">
-        <v>13</v>
-      </c>
       <c r="D17" t="n">
-        <v>8.640000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="E17" t="n">
-        <v>10.69</v>
+        <v>11.43</v>
       </c>
       <c r="F17" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="G17" t="n">
-        <v>15.13</v>
+        <v>20.82</v>
       </c>
       <c r="H17" t="n">
-        <v>1.89</v>
+        <v>2.31</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.44</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1721,63 +1721,63 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>6.78</v>
+        <v>7.1</v>
       </c>
       <c r="E20" t="n">
-        <v>6.44</v>
+        <v>8.25</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="G20" t="n">
-        <v>13.71</v>
+        <v>17.94</v>
       </c>
       <c r="H20" t="n">
-        <v>1.71</v>
+        <v>1.99</v>
       </c>
       <c r="I20" t="n">
-        <v>-7.27</v>
+        <v>-9.69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>6.11</v>
+        <v>6.78</v>
       </c>
       <c r="E21" t="n">
-        <v>6.33</v>
+        <v>6.44</v>
       </c>
       <c r="F21" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>15.37</v>
+        <v>13.71</v>
       </c>
       <c r="H21" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="I21" t="n">
-        <v>-9.039999999999999</v>
+        <v>-7.27</v>
       </c>
     </row>
   </sheetData>
@@ -1875,63 +1875,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>15.4</v>
+        <v>15.72</v>
       </c>
       <c r="E3" t="n">
-        <v>18.65</v>
+        <v>12.21</v>
       </c>
       <c r="F3" t="n">
-        <v>2.66</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>7.92</v>
+        <v>3.73</v>
       </c>
       <c r="H3" t="n">
-        <v>1.13</v>
+        <v>0.53</v>
       </c>
       <c r="I3" t="n">
-        <v>10.73</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>14.65</v>
+        <v>15.4</v>
       </c>
       <c r="E4" t="n">
-        <v>11.61</v>
+        <v>18.65</v>
       </c>
       <c r="F4" t="n">
-        <v>1.93</v>
+        <v>2.66</v>
       </c>
       <c r="G4" t="n">
-        <v>2.92</v>
+        <v>7.92</v>
       </c>
       <c r="H4" t="n">
-        <v>0.49</v>
+        <v>1.13</v>
       </c>
       <c r="I4" t="n">
-        <v>8.69</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="5">
@@ -1968,125 +1968,125 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>10.94</v>
+        <v>12.58</v>
       </c>
       <c r="E6" t="n">
-        <v>13.4</v>
+        <v>14.17</v>
       </c>
       <c r="F6" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>9.02</v>
+        <v>9.18</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="I6" t="n">
-        <v>4.38</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>10.67</v>
+        <v>11.91</v>
       </c>
       <c r="E7" t="n">
-        <v>11.56</v>
+        <v>15.51</v>
       </c>
       <c r="F7" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="G7" t="n">
-        <v>7.26</v>
+        <v>11.78</v>
       </c>
       <c r="H7" t="n">
-        <v>1.21</v>
+        <v>1.68</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>10.41</v>
+        <v>11.58</v>
       </c>
       <c r="E8" t="n">
-        <v>10.94</v>
+        <v>12.07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>10.84</v>
+        <v>9.52</v>
       </c>
       <c r="H8" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>10.03</v>
+        <v>10.41</v>
       </c>
       <c r="E9" t="n">
-        <v>11.25</v>
+        <v>10.94</v>
       </c>
       <c r="F9" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="G9" t="n">
-        <v>8.92</v>
+        <v>10.84</v>
       </c>
       <c r="H9" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="I9" t="n">
-        <v>2.33</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -2154,94 +2154,94 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>7.63</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>7.45</v>
+        <v>11.2</v>
       </c>
       <c r="F12" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>8.25</v>
+        <v>13.09</v>
       </c>
       <c r="H12" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7.42</v>
+        <v>7.63</v>
       </c>
       <c r="E13" t="n">
-        <v>11.84</v>
+        <v>7.45</v>
       </c>
       <c r="F13" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="G13" t="n">
-        <v>16.35</v>
+        <v>8.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.34</v>
+        <v>1.38</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.51</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>7.19</v>
+        <v>7.42</v>
       </c>
       <c r="E14" t="n">
-        <v>8.44</v>
+        <v>11.84</v>
       </c>
       <c r="F14" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="G14" t="n">
-        <v>10.98</v>
+        <v>16.35</v>
       </c>
       <c r="H14" t="n">
-        <v>1.83</v>
+        <v>2.34</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.54</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="15">
@@ -2340,125 +2340,125 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>5.2</v>
+        <v>5.86</v>
       </c>
       <c r="E18" t="n">
-        <v>7.66</v>
+        <v>11.84</v>
       </c>
       <c r="F18" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="G18" t="n">
-        <v>12.97</v>
+        <v>17.4</v>
       </c>
       <c r="H18" t="n">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.31</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>4.24</v>
+        <v>5.24</v>
       </c>
       <c r="E19" t="n">
-        <v>6.76</v>
+        <v>8.25</v>
       </c>
       <c r="F19" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="G19" t="n">
-        <v>13.39</v>
+        <v>17.33</v>
       </c>
       <c r="H19" t="n">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.63</v>
+        <v>-9.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Parma Calcio 1913</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>3.51</v>
+        <v>5.1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.67</v>
+        <v>8.68</v>
       </c>
       <c r="F20" t="n">
-        <v>0.78</v>
+        <v>1.24</v>
       </c>
       <c r="G20" t="n">
-        <v>12.72</v>
+        <v>16.01</v>
       </c>
       <c r="H20" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="I20" t="n">
-        <v>-8.050000000000001</v>
+        <v>-7.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Parma Calcio 1913</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2.92</v>
+        <v>3.51</v>
       </c>
       <c r="E21" t="n">
-        <v>7.48</v>
+        <v>4.67</v>
       </c>
       <c r="F21" t="n">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="G21" t="n">
-        <v>16.81</v>
+        <v>12.72</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="I21" t="n">
-        <v>-9.33</v>
+        <v>-8.050000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2556,125 +2556,125 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>12.01</v>
+        <v>12.98</v>
       </c>
       <c r="E3" t="n">
-        <v>12.2</v>
+        <v>14.58</v>
       </c>
       <c r="F3" t="n">
-        <v>2.03</v>
+        <v>2.43</v>
       </c>
       <c r="G3" t="n">
-        <v>6.03</v>
+        <v>6.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="I3" t="n">
-        <v>6.17</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>11.65</v>
+        <v>12.09</v>
       </c>
       <c r="E4" t="n">
-        <v>14.25</v>
+        <v>11.46</v>
       </c>
       <c r="F4" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="G4" t="n">
-        <v>8.9</v>
+        <v>6.26</v>
       </c>
       <c r="H4" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>11.23</v>
+        <v>12.01</v>
       </c>
       <c r="E5" t="n">
-        <v>10.26</v>
+        <v>12.2</v>
       </c>
       <c r="F5" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="G5" t="n">
-        <v>4.41</v>
+        <v>6.03</v>
       </c>
       <c r="H5" t="n">
-        <v>0.88</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>5.85</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>11.65</v>
       </c>
       <c r="E6" t="n">
-        <v>12.73</v>
+        <v>14.25</v>
       </c>
       <c r="F6" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>8.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="I6" t="n">
-        <v>7.13</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="7">
@@ -2711,156 +2711,156 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC Cologne</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>8.69</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>11.51</v>
+        <v>11.82</v>
       </c>
       <c r="F8" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="G8" t="n">
-        <v>11.01</v>
+        <v>10.62</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>FC Cologne</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7.31</v>
+        <v>8.69</v>
       </c>
       <c r="E9" t="n">
-        <v>12.1</v>
+        <v>11.51</v>
       </c>
       <c r="F9" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="G9" t="n">
-        <v>14.66</v>
+        <v>11.01</v>
       </c>
       <c r="H9" t="n">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.56</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>7.25</v>
+        <v>7.31</v>
       </c>
       <c r="E10" t="n">
-        <v>13.33</v>
+        <v>12.1</v>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>15.77</v>
+        <v>14.66</v>
       </c>
       <c r="H10" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.44</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>VfB Stuttgart</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="E11" t="n">
-        <v>8.800000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="F11" t="n">
-        <v>1.47</v>
+        <v>2.22</v>
       </c>
       <c r="G11" t="n">
-        <v>10.31</v>
+        <v>15.77</v>
       </c>
       <c r="H11" t="n">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.51</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>6.62</v>
+        <v>7.19</v>
       </c>
       <c r="E12" t="n">
-        <v>9.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="G12" t="n">
-        <v>9.859999999999999</v>
+        <v>10.31</v>
       </c>
       <c r="H12" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.21</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="13">
@@ -3056,28 +3056,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.78</v>
+        <v>4.18</v>
       </c>
       <c r="E19" t="n">
-        <v>8.52</v>
+        <v>9.27</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="G19" t="n">
-        <v>13.96</v>
+        <v>16.13</v>
       </c>
       <c r="H19" t="n">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.44</v>
+        <v>-6.86</v>
       </c>
     </row>
   </sheetData>
@@ -3144,7 +3144,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -3154,59 +3154,59 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>14.03</v>
+        <v>14.22</v>
       </c>
       <c r="E2" t="n">
-        <v>18.03</v>
+        <v>13.39</v>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>10.36</v>
+        <v>6.78</v>
       </c>
       <c r="H2" t="n">
-        <v>1.48</v>
+        <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>7.67</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>13.04</v>
+        <v>14.03</v>
       </c>
       <c r="E3" t="n">
-        <v>15.67</v>
+        <v>18.03</v>
       </c>
       <c r="F3" t="n">
-        <v>2.24</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>9.029999999999999</v>
+        <v>10.36</v>
       </c>
       <c r="H3" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="I3" t="n">
-        <v>6.64</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3216,53 +3216,53 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>12.99</v>
+        <v>13.04</v>
       </c>
       <c r="E4" t="n">
-        <v>14.07</v>
+        <v>15.67</v>
       </c>
       <c r="F4" t="n">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
-        <v>10.14</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="I4" t="n">
-        <v>3.93</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>12.84</v>
+        <v>12.99</v>
       </c>
       <c r="E5" t="n">
-        <v>10.33</v>
+        <v>14.07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="G5" t="n">
-        <v>3.77</v>
+        <v>10.14</v>
       </c>
       <c r="H5" t="n">
-        <v>0.63</v>
+        <v>1.45</v>
       </c>
       <c r="I5" t="n">
-        <v>6.56</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="6">
@@ -3299,7 +3299,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3309,239 +3309,239 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>10.22</v>
+        <v>12.05</v>
       </c>
       <c r="E7" t="n">
-        <v>10.78</v>
+        <v>12.69</v>
       </c>
       <c r="F7" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="G7" t="n">
-        <v>10.53</v>
+        <v>8.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="I7" t="n">
-        <v>0.25</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>10.21</v>
+        <v>11.18</v>
       </c>
       <c r="E8" t="n">
-        <v>10.99</v>
+        <v>16.44</v>
       </c>
       <c r="F8" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="G8" t="n">
-        <v>7.31</v>
+        <v>14.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.22</v>
+        <v>2.13</v>
       </c>
       <c r="I8" t="n">
-        <v>3.68</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.22</v>
       </c>
       <c r="E9" t="n">
-        <v>13.43</v>
+        <v>10.78</v>
       </c>
       <c r="F9" t="n">
-        <v>2.24</v>
+        <v>1.54</v>
       </c>
       <c r="G9" t="n">
-        <v>11.84</v>
+        <v>10.53</v>
       </c>
       <c r="H9" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1.59</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>7.99</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="G10" t="n">
-        <v>7.98</v>
+        <v>7.55</v>
       </c>
       <c r="H10" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.58</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>7.5</v>
+        <v>8.99</v>
       </c>
       <c r="E11" t="n">
-        <v>9.56</v>
+        <v>12.88</v>
       </c>
       <c r="F11" t="n">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>11.59</v>
+        <v>15.23</v>
       </c>
       <c r="H11" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.03</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>7.34</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>6.28</v>
+        <v>7.89</v>
       </c>
       <c r="F12" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="G12" t="n">
-        <v>7.07</v>
+        <v>9.73</v>
       </c>
       <c r="H12" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.79</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>6.73</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>9.77</v>
+        <v>10.01</v>
       </c>
       <c r="F13" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="G13" t="n">
-        <v>13.42</v>
+        <v>14.27</v>
       </c>
       <c r="H13" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.65</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>6.56</v>
+        <v>8.06</v>
       </c>
       <c r="E14" t="n">
-        <v>8.050000000000001</v>
+        <v>11.36</v>
       </c>
       <c r="F14" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>12.68</v>
+        <v>14.69</v>
       </c>
       <c r="H14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.63</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="15">
@@ -3551,152 +3551,152 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5</v>
+        <v>7.36</v>
       </c>
       <c r="E15" t="n">
-        <v>7.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F15" t="n">
         <v>1.17</v>
       </c>
       <c r="G15" t="n">
-        <v>10.25</v>
+        <v>11.95</v>
       </c>
       <c r="H15" t="n">
         <v>1.71</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.24</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>6.27</v>
+        <v>6.44</v>
       </c>
       <c r="E16" t="n">
-        <v>8.91</v>
+        <v>8.99</v>
       </c>
       <c r="F16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G16" t="n">
-        <v>13.64</v>
+        <v>13.57</v>
       </c>
       <c r="H16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.73</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>5.93</v>
+        <v>6.27</v>
       </c>
       <c r="E17" t="n">
-        <v>10.62</v>
+        <v>8.91</v>
       </c>
       <c r="F17" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="G17" t="n">
-        <v>16.75</v>
+        <v>13.64</v>
       </c>
       <c r="H17" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.13</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>5.71</v>
+        <v>5.93</v>
       </c>
       <c r="E18" t="n">
-        <v>8.23</v>
+        <v>10.62</v>
       </c>
       <c r="F18" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="G18" t="n">
-        <v>13.53</v>
+        <v>16.75</v>
       </c>
       <c r="H18" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.3</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>5.34</v>
+        <v>5.71</v>
       </c>
       <c r="E19" t="n">
-        <v>7.4</v>
+        <v>8.23</v>
       </c>
       <c r="F19" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="G19" t="n">
-        <v>11.61</v>
+        <v>13.53</v>
       </c>
       <c r="H19" t="n">
         <v>1.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.21</v>
+        <v>-5.3</v>
       </c>
     </row>
   </sheetData>

--- a/understat_all_leagues_advanced.xlsx
+++ b/understat_all_leagues_advanced.xlsx
@@ -854,249 +854,249 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>8.460000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>11.04</v>
+        <v>8.83</v>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="G14" t="n">
-        <v>14.88</v>
+        <v>11.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.13</v>
+        <v>1.6</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.84</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>7.97</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>8.91</v>
+        <v>11.04</v>
       </c>
       <c r="F15" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>13.06</v>
+        <v>14.88</v>
       </c>
       <c r="H15" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.15</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>7.7</v>
+        <v>7.97</v>
       </c>
       <c r="E16" t="n">
-        <v>7.85</v>
+        <v>8.91</v>
       </c>
       <c r="F16" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="G16" t="n">
-        <v>10.06</v>
+        <v>13.06</v>
       </c>
       <c r="H16" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.21</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>6.84</v>
+        <v>7.03</v>
       </c>
       <c r="E17" t="n">
-        <v>9.75</v>
+        <v>7.78</v>
       </c>
       <c r="F17" t="n">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="G17" t="n">
-        <v>16.09</v>
+        <v>11.78</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.34</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>6.67</v>
+        <v>6.84</v>
       </c>
       <c r="E18" t="n">
-        <v>8.68</v>
+        <v>9.75</v>
       </c>
       <c r="F18" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="G18" t="n">
-        <v>13.09</v>
+        <v>16.09</v>
       </c>
       <c r="H18" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.41</v>
+        <v>-6.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>6.22</v>
+        <v>6.67</v>
       </c>
       <c r="E19" t="n">
-        <v>10.46</v>
+        <v>8.68</v>
       </c>
       <c r="F19" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="G19" t="n">
-        <v>16.04</v>
+        <v>13.09</v>
       </c>
       <c r="H19" t="n">
-        <v>2.29</v>
+        <v>1.87</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.58</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>6.15</v>
+        <v>6.22</v>
       </c>
       <c r="E20" t="n">
-        <v>7.39</v>
+        <v>10.46</v>
       </c>
       <c r="F20" t="n">
-        <v>1.06</v>
+        <v>1.49</v>
       </c>
       <c r="G20" t="n">
-        <v>12.26</v>
+        <v>16.04</v>
       </c>
       <c r="H20" t="n">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.87</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="E21" t="n">
-        <v>6.64</v>
+        <v>7.39</v>
       </c>
       <c r="F21" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="G21" t="n">
-        <v>10.81</v>
+        <v>12.26</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.17</v>
+        <v>-4.87</v>
       </c>
     </row>
   </sheetData>
@@ -1566,218 +1566,218 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="n">
         <v>9</v>
       </c>
-      <c r="C15" t="n">
-        <v>6</v>
-      </c>
       <c r="D15" t="n">
-        <v>10.07</v>
+        <v>10.08</v>
       </c>
       <c r="E15" t="n">
-        <v>9.69</v>
+        <v>11.41</v>
       </c>
       <c r="F15" t="n">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="G15" t="n">
-        <v>14.59</v>
+        <v>13.93</v>
       </c>
       <c r="H15" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.9</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>9.24</v>
+        <v>10.07</v>
       </c>
       <c r="E16" t="n">
-        <v>10.78</v>
+        <v>9.69</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="G16" t="n">
-        <v>18.42</v>
+        <v>14.59</v>
       </c>
       <c r="H16" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-7.64</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>9.19</v>
+        <v>9.24</v>
       </c>
       <c r="E17" t="n">
-        <v>11.43</v>
+        <v>10.78</v>
       </c>
       <c r="F17" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>20.82</v>
+        <v>18.42</v>
       </c>
       <c r="H17" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="I17" t="n">
-        <v>-9.390000000000001</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="n">
         <v>8</v>
       </c>
-      <c r="C18" t="n">
-        <v>7</v>
-      </c>
       <c r="D18" t="n">
-        <v>7.73</v>
+        <v>9.19</v>
       </c>
       <c r="E18" t="n">
-        <v>11.88</v>
+        <v>11.43</v>
       </c>
       <c r="F18" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="G18" t="n">
-        <v>17.96</v>
+        <v>20.82</v>
       </c>
       <c r="H18" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="I18" t="n">
-        <v>-6.08</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>7.69</v>
+        <v>7.73</v>
       </c>
       <c r="E19" t="n">
-        <v>9.119999999999999</v>
+        <v>11.88</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="G19" t="n">
-        <v>13.03</v>
+        <v>17.96</v>
       </c>
       <c r="H19" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.91</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>7.1</v>
+        <v>7.22</v>
       </c>
       <c r="E20" t="n">
-        <v>8.25</v>
+        <v>7.34</v>
       </c>
       <c r="F20" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="G20" t="n">
-        <v>17.94</v>
+        <v>16</v>
       </c>
       <c r="H20" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="I20" t="n">
-        <v>-9.69</v>
+        <v>-8.66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>6.78</v>
+        <v>7.1</v>
       </c>
       <c r="E21" t="n">
-        <v>6.44</v>
+        <v>8.25</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="G21" t="n">
-        <v>13.71</v>
+        <v>17.94</v>
       </c>
       <c r="H21" t="n">
-        <v>1.71</v>
+        <v>1.99</v>
       </c>
       <c r="I21" t="n">
-        <v>-7.27</v>
+        <v>-9.69</v>
       </c>
     </row>
   </sheetData>
@@ -2096,28 +2096,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>9.44</v>
+        <v>10.25</v>
       </c>
       <c r="E10" t="n">
-        <v>11.22</v>
+        <v>13.05</v>
       </c>
       <c r="F10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>9.619999999999999</v>
+        <v>12.35</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
@@ -2154,69 +2154,69 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="E12" t="n">
-        <v>11.2</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="G12" t="n">
-        <v>13.09</v>
+        <v>9.52</v>
       </c>
       <c r="H12" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.89</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>7.63</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>7.45</v>
+        <v>11.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>8.25</v>
+        <v>13.09</v>
       </c>
       <c r="H13" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2226,115 +2226,115 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>7.42</v>
+        <v>8.02</v>
       </c>
       <c r="E14" t="n">
-        <v>11.84</v>
+        <v>8.99</v>
       </c>
       <c r="F14" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="G14" t="n">
-        <v>16.35</v>
+        <v>12.99</v>
       </c>
       <c r="H14" t="n">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.51</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>7.02</v>
+        <v>7.42</v>
       </c>
       <c r="E15" t="n">
-        <v>12.41</v>
+        <v>11.84</v>
       </c>
       <c r="F15" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="G15" t="n">
-        <v>17.84</v>
+        <v>16.35</v>
       </c>
       <c r="H15" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.43</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7.01</v>
+        <v>7.02</v>
       </c>
       <c r="E16" t="n">
-        <v>6.7</v>
+        <v>12.41</v>
       </c>
       <c r="F16" t="n">
-        <v>0.96</v>
+        <v>1.77</v>
       </c>
       <c r="G16" t="n">
-        <v>10.08</v>
+        <v>17.84</v>
       </c>
       <c r="H16" t="n">
-        <v>1.44</v>
+        <v>2.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.38</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>6.03</v>
+        <v>7.01</v>
       </c>
       <c r="E17" t="n">
-        <v>6.26</v>
+        <v>6.7</v>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="G17" t="n">
-        <v>11.15</v>
+        <v>10.08</v>
       </c>
       <c r="H17" t="n">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.89</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="18">
@@ -2437,28 +2437,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3.51</v>
+        <v>4.77</v>
       </c>
       <c r="E21" t="n">
-        <v>4.67</v>
+        <v>5.94</v>
       </c>
       <c r="F21" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="G21" t="n">
-        <v>12.72</v>
+        <v>14.05</v>
       </c>
       <c r="H21" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="I21" t="n">
-        <v>-8.050000000000001</v>
+        <v>-8.109999999999999</v>
       </c>
     </row>
   </sheetData>
